--- a/02_DIA_inicio_2026_analisis_assets/rbd_9416_escuela-poetas-de-chile_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9416_escuela-poetas-de-chile_nt1_rubricas.xlsx
@@ -1872,13 +1872,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C55EFAF2-38F1-4426-B1AD-2568E7BE6C12}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DB84F64-F95D-456B-9874-55744BFE2E00}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BD1E685-7D86-4B53-BCA9-3929008877F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6390B1E-27DF-4C94-8457-512EAFE7393C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F25DBF4-23B5-4049-8C02-842B39000310}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CCD7518-40D1-41F6-A067-F3C4D8CFD896}"/>
 </file>